--- a/data/trans_orig/P36B04-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B04-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de legumbres en 2007</t>
+          <t>Población según la frecuencia de consumo de legumbres en 2007 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>810</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54587</t>
+          <t>55327</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85388</t>
+          <t>87755</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15515</t>
+          <t>15062</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34340</t>
+          <t>35346</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75392</t>
+          <t>74219</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111831</t>
+          <t>112510</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>263484</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>310335</t>
+          <t>307341</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>189587</t>
+          <t>187431</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>219666</t>
+          <t>218420</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>458266</t>
+          <t>463471</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>515930</t>
+          <t>516948</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,34%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90397</t>
+          <t>91809</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>130500</t>
+          <t>128924</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55543</t>
+          <t>55896</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82957</t>
+          <t>84026</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>155783</t>
+          <t>154412</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>203916</t>
+          <t>203302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12539</t>
+          <t>13183</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21591</t>
+          <t>22410</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17458</t>
+          <t>16083</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14392</t>
+          <t>14088</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9108</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24791</t>
+          <t>25953</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39525</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66854</t>
+          <t>65148</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38301</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64760</t>
+          <t>64895</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86248</t>
+          <t>85920</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123728</t>
+          <t>123280</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,69%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>205981</t>
+          <t>205041</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>242977</t>
+          <t>242411</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>216752</t>
+          <t>216768</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>253628</t>
+          <t>253800</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>435383</t>
+          <t>432702</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>488658</t>
+          <t>485964</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>65,78%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65056</t>
+          <t>66337</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98156</t>
+          <t>98401</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59364</t>
+          <t>59878</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90602</t>
+          <t>90593</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132461</t>
+          <t>133462</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>178652</t>
+          <t>177383</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10242</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10904</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15872</t>
+          <t>15650</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47746</t>
+          <t>48741</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79797</t>
+          <t>78820</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10218</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24843</t>
+          <t>24257</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61270</t>
+          <t>64685</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>95477</t>
+          <t>97152</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>302579</t>
+          <t>304337</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>352034</t>
+          <t>350439</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>84158</t>
+          <t>84157</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>108367</t>
+          <t>109185</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>396395</t>
+          <t>398256</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>450160</t>
+          <t>450268</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,4%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>118455</t>
+          <t>119339</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>160017</t>
+          <t>160775</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34477</t>
+          <t>34975</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57337</t>
+          <t>58433</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>159992</t>
+          <t>162091</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>209290</t>
+          <t>205141</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18257</t>
+          <t>19325</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10352</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8385</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24451</t>
+          <t>23534</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21161</t>
+          <t>21689</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20185</t>
+          <t>19204</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14751</t>
+          <t>14657</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33976</t>
+          <t>32674</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>117515</t>
+          <t>118631</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>161298</t>
+          <t>164904</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>51498</t>
+          <t>50606</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>82848</t>
+          <t>81090</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>178160</t>
+          <t>178170</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>229962</t>
+          <t>230753</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>681301</t>
+          <t>679757</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>748330</t>
+          <t>749434</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>395117</t>
+          <t>396509</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>445017</t>
+          <t>447177</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1090794</t>
+          <t>1087115</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1177956</t>
+          <t>1182205</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,54%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>323689</t>
+          <t>323354</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>384806</t>
+          <t>389448</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>182472</t>
+          <t>183630</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>230778</t>
+          <t>231322</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>521142</t>
+          <t>519891</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>600285</t>
+          <t>601091</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11611</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27373</t>
+          <t>27822</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,47 +3245,47 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>12077</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>6685</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>19768</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>12077</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>19609</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20967</t>
+          <t>21487</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41726</t>
+          <t>41775</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12194</t>
+          <t>11429</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14771</t>
+          <t>16235</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21829</t>
+          <t>21380</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>32811</t>
+          <t>33055</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>59785</t>
+          <t>59717</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21157</t>
+          <t>22026</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>43949</t>
+          <t>44860</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>60244</t>
+          <t>62331</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>95060</t>
+          <t>95361</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>179185</t>
+          <t>175168</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>217033</t>
+          <t>213801</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>311090</t>
+          <t>310470</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>358941</t>
+          <t>358637</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>499443</t>
+          <t>502013</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>561337</t>
+          <t>565450</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>82574</t>
+          <t>80580</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>115747</t>
+          <t>116605</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>165006</t>
+          <t>163514</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>210189</t>
+          <t>209198</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>257145</t>
+          <t>255325</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>310677</t>
+          <t>313075</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,09%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12708</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>15876</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>23265</t>
+          <t>22219</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13240</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22532</t>
+          <t>22805</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>31269</t>
+          <t>32135</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>35899</t>
+          <t>37426</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>60181</t>
+          <t>61587</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>94875</t>
+          <t>95332</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>135762</t>
+          <t>135720</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>139185</t>
+          <t>139543</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>186975</t>
+          <t>185527</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>168483</t>
+          <t>170861</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>201460</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>790859</t>
+          <t>791184</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>856598</t>
+          <t>859484</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>969642</t>
+          <t>970108</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1044617</t>
+          <t>1042248</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,46%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>41583</t>
+          <t>41137</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>68288</t>
+          <t>66711</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>252529</t>
+          <t>252696</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>311351</t>
+          <t>309457</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>303484</t>
+          <t>304024</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>370280</t>
+          <t>366443</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>22617</t>
+          <t>22445</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>29369</t>
+          <t>28871</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>27627</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>52358</t>
+          <t>54974</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,82 +4839,82 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>47430</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>35424</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>63434</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>85707</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>67930</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>106018</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
           <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>47430</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>35331</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>65253</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>85707</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>67309</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>104328</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>377068</t>
+          <t>372154</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>452105</t>
+          <t>455569</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>266422</t>
+          <t>271551</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>333070</t>
+          <t>334834</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>663341</t>
+          <t>666370</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>762866</t>
+          <t>770564</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1880227</t>
+          <t>1880978</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1990513</t>
+          <t>1992637</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2061881</t>
+          <t>2057912</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2179496</t>
+          <t>2169845</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3975171</t>
+          <t>3970415</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4129999</t>
+          <t>4129622</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,15%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>782935</t>
+          <t>784011</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>884169</t>
+          <t>881643</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>814912</t>
+          <t>814225</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>916274</t>
+          <t>911346</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1630162</t>
+          <t>1622299</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1765060</t>
+          <t>1770573</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>34051</t>
+          <t>34779</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>62290</t>
+          <t>63241</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>35261</t>
+          <t>35882</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>63506</t>
+          <t>63544</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>75634</t>
+          <t>76727</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>113297</t>
+          <t>115752</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de legumbres en 2012</t>
+          <t>Población según la frecuencia de consumo de legumbres en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12331</t>
+          <t>10923</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16713</t>
+          <t>16677</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23017</t>
+          <t>22861</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27053</t>
+          <t>27294</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51242</t>
+          <t>49728</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29868</t>
+          <t>29611</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55410</t>
+          <t>56775</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61971</t>
+          <t>62777</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97137</t>
+          <t>98383</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>237371</t>
+          <t>234408</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>280269</t>
+          <t>280718</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>175571</t>
+          <t>172910</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>211119</t>
+          <t>210261</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>422034</t>
+          <t>423870</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>479330</t>
+          <t>480261</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,26%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103849</t>
+          <t>103689</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143392</t>
+          <t>146327</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50262</t>
+          <t>50170</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81205</t>
+          <t>80008</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>162998</t>
+          <t>163270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>210413</t>
+          <t>214210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20995</t>
+          <t>21415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10966</t>
+          <t>10032</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9633</t>
+          <t>9213</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26814</t>
+          <t>27302</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>982</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>16200</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25786</t>
+          <t>25233</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50773</t>
+          <t>50536</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17436</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39291</t>
+          <t>38385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48011</t>
+          <t>48225</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81801</t>
+          <t>81463</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>230615</t>
+          <t>230661</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>274091</t>
+          <t>275477</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>194859</t>
+          <t>196012</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>232165</t>
+          <t>232870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>440713</t>
+          <t>440029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>497081</t>
+          <t>497336</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,89%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97217</t>
+          <t>95535</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>135168</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61325</t>
+          <t>62236</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92053</t>
+          <t>94817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>168134</t>
+          <t>165933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>218300</t>
+          <t>214941</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17242</t>
+          <t>15748</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8987</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26681</t>
+          <t>26487</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14336</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36226</t>
+          <t>37985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10053</t>
+          <t>10626</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28979</t>
+          <t>28178</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55180</t>
+          <t>53599</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14249</t>
+          <t>13393</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32966</t>
+          <t>32572</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48298</t>
+          <t>46739</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79679</t>
+          <t>79322</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>368731</t>
+          <t>368367</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>418788</t>
+          <t>418960</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>142412</t>
+          <t>145546</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>175952</t>
+          <t>176891</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>520773</t>
+          <t>525364</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>580590</t>
+          <t>582261</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,6%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>154479</t>
+          <t>156372</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>202688</t>
+          <t>203050</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57385</t>
+          <t>56206</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87346</t>
+          <t>85691</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>224655</t>
+          <t>225383</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>282960</t>
+          <t>276706</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22540</t>
+          <t>22248</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9830</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27157</t>
+          <t>27470</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>11091</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30731</t>
+          <t>28815</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13735</t>
+          <t>13506</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33985</t>
+          <t>34090</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30057</t>
+          <t>28657</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55736</t>
+          <t>55899</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>78187</t>
+          <t>76705</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>117572</t>
+          <t>118365</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>49984</t>
+          <t>50652</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>80396</t>
+          <t>82641</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>135424</t>
+          <t>136909</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>186707</t>
+          <t>186258</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>638153</t>
+          <t>641137</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>708262</t>
+          <t>712268</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424343</t>
+          <t>424177</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>479000</t>
+          <t>478802</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1078134</t>
+          <t>1084478</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1168595</t>
+          <t>1174161</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>61,14%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>302325</t>
+          <t>302752</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>371356</t>
+          <t>366493</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>175266</t>
+          <t>176293</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>223997</t>
+          <t>224754</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>495104</t>
+          <t>493510</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>576750</t>
+          <t>573406</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21696</t>
+          <t>21576</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43766</t>
+          <t>44707</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16730</t>
+          <t>16426</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38701</t>
+          <t>37921</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>44521</t>
+          <t>42978</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>76361</t>
+          <t>76532</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15490</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21336</t>
+          <t>20259</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11043</t>
+          <t>11790</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30791</t>
+          <t>30931</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25723</t>
+          <t>25615</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>48987</t>
+          <t>49109</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>39081</t>
+          <t>39616</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69651</t>
+          <t>71991</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>71783</t>
+          <t>70863</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>109675</t>
+          <t>110923</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>306007</t>
+          <t>306400</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>346918</t>
+          <t>351116</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>412727</t>
+          <t>409367</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>469808</t>
+          <t>466255</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>731433</t>
+          <t>728158</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>800749</t>
+          <t>802792</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,26%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>109006</t>
+          <t>106272</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>148037</t>
+          <t>147493</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>200252</t>
+          <t>201663</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>249286</t>
+          <t>251327</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>317429</t>
+          <t>321409</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>385022</t>
+          <t>387654</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>19216</t>
+          <t>18889</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20545</t>
+          <t>19411</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>42348</t>
+          <t>43027</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>29891</t>
+          <t>29542</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>53726</t>
+          <t>56024</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16356</t>
+          <t>15367</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25499</t>
+          <t>25601</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14498</t>
+          <t>14951</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>34998</t>
+          <t>36947</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>25256</t>
+          <t>24732</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>46166</t>
+          <t>46294</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>87658</t>
+          <t>88253</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>126544</t>
+          <t>126922</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>118273</t>
+          <t>115720</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>164782</t>
+          <t>161137</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>162936</t>
+          <t>163362</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>192980</t>
+          <t>193706</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>672112</t>
+          <t>667717</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>735526</t>
+          <t>733617</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>845887</t>
+          <t>843925</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>917818</t>
+          <t>919051</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>28949</t>
+          <t>28656</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>52780</t>
+          <t>51696</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>233381</t>
+          <t>231220</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>290566</t>
+          <t>289892</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>268458</t>
+          <t>271528</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>331706</t>
+          <t>331933</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>979</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>8981</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>12276</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>31121</t>
+          <t>30918</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>15595</t>
+          <t>16288</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>35433</t>
+          <t>35194</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>33926</t>
+          <t>34312</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>61800</t>
+          <t>62119</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>47494</t>
+          <t>48908</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>80348</t>
+          <t>83492</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>89916</t>
+          <t>90203</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>134668</t>
+          <t>132826</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>249479</t>
+          <t>247848</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>313437</t>
+          <t>313612</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>281296</t>
+          <t>278331</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>348383</t>
+          <t>350638</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>543755</t>
+          <t>545414</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>639636</t>
+          <t>640659</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2026808</t>
+          <t>2030926</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2140597</t>
+          <t>2143450</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2103333</t>
+          <t>2100053</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2219985</t>
+          <t>2223377</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4168711</t>
+          <t>4165459</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4335620</t>
+          <t>4331093</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,32%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>870647</t>
+          <t>864692</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>976663</t>
+          <t>971912</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>845354</t>
+          <t>840046</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>949164</t>
+          <t>952201</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1743466</t>
+          <t>1742572</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1897060</t>
+          <t>1895703</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>61991</t>
+          <t>61444</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>98765</t>
+          <t>98844</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>82454</t>
+          <t>83243</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>123147</t>
+          <t>122960</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>152247</t>
+          <t>155303</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>209452</t>
+          <t>209637</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de legumbres en 2016</t>
+          <t>Población según la frecuencia de consumo de legumbres en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>7558</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10263</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3091</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13979</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34282</t>
+          <t>33999</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61623</t>
+          <t>62941</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28274</t>
+          <t>28194</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52046</t>
+          <t>53265</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69496</t>
+          <t>67997</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106287</t>
+          <t>104851</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>219444</t>
+          <t>220042</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>262671</t>
+          <t>265421</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>198699</t>
+          <t>195877</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>234794</t>
+          <t>233926</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>429288</t>
+          <t>431646</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>485418</t>
+          <t>486507</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,78%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>110661</t>
+          <t>107204</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>150190</t>
+          <t>148358</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70123</t>
+          <t>70472</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103690</t>
+          <t>104430</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>190077</t>
+          <t>188739</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>237806</t>
+          <t>238295</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15004</t>
+          <t>14816</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>16685</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10828</t>
+          <t>10134</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14851</t>
+          <t>15709</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21031</t>
+          <t>21828</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28929</t>
+          <t>28460</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54405</t>
+          <t>53890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29406</t>
+          <t>31551</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56437</t>
+          <t>56794</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66680</t>
+          <t>66158</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>104030</t>
+          <t>101711</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>195836</t>
+          <t>200722</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>237528</t>
+          <t>238221</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183378</t>
+          <t>185282</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>224122</t>
+          <t>225758</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>397634</t>
+          <t>394639</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>451869</t>
+          <t>450171</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,39%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89402</t>
+          <t>89178</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125650</t>
+          <t>123684</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86579</t>
+          <t>85062</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121593</t>
+          <t>119630</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>184377</t>
+          <t>185731</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>235702</t>
+          <t>235935</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,65%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11608</t>
+          <t>13553</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,47 +11897,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>11456</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5796</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>21136</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>3,09%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>11456</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>6125</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>21397</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9694</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27909</t>
+          <t>26206</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14864</t>
+          <t>14906</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>16927</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30130</t>
+          <t>30170</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55365</t>
+          <t>57028</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>13056</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>30030</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47362</t>
+          <t>48430</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78810</t>
+          <t>78335</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>278216</t>
+          <t>277775</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>324357</t>
+          <t>322959</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>73888</t>
+          <t>74087</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>100362</t>
+          <t>98957</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,47 +12388,47 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
+          <t>59,57%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>388842</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>361441</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>414396</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>56,69%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>52,69%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
           <t>60,41%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>388842</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>360733</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>412871</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>56,69%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>52,59%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>60,19%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>138851</t>
+          <t>141127</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>181385</t>
+          <t>183169</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42141</t>
+          <t>42172</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67804</t>
+          <t>66766</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>191020</t>
+          <t>191105</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>239393</t>
+          <t>240056</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,0%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>17099</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19483</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14545</t>
+          <t>14693</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29386</t>
+          <t>26965</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15564</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35868</t>
+          <t>35222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>85841</t>
+          <t>86272</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>125349</t>
+          <t>123926</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>73395</t>
+          <t>72544</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>110006</t>
+          <t>108653</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>167557</t>
+          <t>170702</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>222142</t>
+          <t>222753</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>585074</t>
+          <t>586816</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>652107</t>
+          <t>653539</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>402732</t>
+          <t>405694</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>460884</t>
+          <t>465252</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1010871</t>
+          <t>1006654</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1101132</t>
+          <t>1100049</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>342936</t>
+          <t>344341</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>406510</t>
+          <t>406924</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>232515</t>
+          <t>229609</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>285936</t>
+          <t>284100</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>589317</t>
+          <t>591656</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>674504</t>
+          <t>677858</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25192</t>
+          <t>24955</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>51042</t>
+          <t>49863</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14689</t>
+          <t>14763</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33294</t>
+          <t>34502</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>44913</t>
+          <t>44425</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>75307</t>
+          <t>75506</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16242</t>
+          <t>17586</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24282</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>47833</t>
+          <t>49833</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>77237</t>
+          <t>80052</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>46720</t>
+          <t>46969</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>77242</t>
+          <t>79186</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>103790</t>
+          <t>102535</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>148006</t>
+          <t>148224</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>299782</t>
+          <t>295081</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>349968</t>
+          <t>348538</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>365793</t>
+          <t>364160</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>421846</t>
+          <t>418300</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>677413</t>
+          <t>679148</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>752207</t>
+          <t>754270</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,67%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>193966</t>
+          <t>194024</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>240943</t>
+          <t>241448</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>232497</t>
+          <t>232172</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>287435</t>
+          <t>287815</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>437067</t>
+          <t>440141</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>510626</t>
+          <t>511818</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4284</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17186</t>
+          <t>17271</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9716</t>
+          <t>9588</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28297</t>
+          <t>27804</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>16750</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>39495</t>
+          <t>39054</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>13959</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9496</t>
+          <t>9447</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25673</t>
+          <t>26373</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14688</t>
+          <t>14821</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>34407</t>
+          <t>34362</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,7 +14243,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>31578</t>
+          <t>30514</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>56746</t>
+          <t>55824</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>78674</t>
+          <t>78648</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>116164</t>
+          <t>116423</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>118400</t>
+          <t>118164</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>162446</t>
+          <t>165040</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>136666</t>
+          <t>137662</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>170587</t>
+          <t>171581</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>559086</t>
+          <t>559715</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>627307</t>
+          <t>624969</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>710246</t>
+          <t>711384</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>785600</t>
+          <t>785765</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,65%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>59198</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>89170</t>
+          <t>89636</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>313112</t>
+          <t>313597</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>377871</t>
+          <t>377589</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>382237</t>
+          <t>381347</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>451903</t>
+          <t>454271</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13054</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>18723</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>39778</t>
+          <t>39322</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>24162</t>
+          <t>24360</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>49146</t>
+          <t>49253</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>23487</t>
+          <t>23191</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>47744</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>42953</t>
+          <t>41134</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>72630</t>
+          <t>73234</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>72550</t>
+          <t>72206</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>110253</t>
+          <t>111154</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>302427</t>
+          <t>305829</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>374683</t>
+          <t>375854</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>312034</t>
+          <t>311605</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>383890</t>
+          <t>385975</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>639473</t>
+          <t>635497</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>739248</t>
+          <t>743408</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1799831</t>
+          <t>1798106</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1920757</t>
+          <t>1913493</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1867822</t>
+          <t>1870610</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1989961</t>
+          <t>1991353</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3707429</t>
+          <t>3705386</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3880850</t>
+          <t>3875900</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,26%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1005625</t>
+          <t>1009839</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1113125</t>
+          <t>1123681</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1046736</t>
+          <t>1043324</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1160860</t>
+          <t>1160141</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2083754</t>
+          <t>2081935</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2233557</t>
+          <t>2237373</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,48%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>58868</t>
+          <t>57984</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>95683</t>
+          <t>93084</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>65169</t>
+          <t>67670</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>105123</t>
+          <t>105434</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>135776</t>
+          <t>133112</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>185847</t>
+          <t>188103</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B04-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B04-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7383</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9012</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12162</t>
+          <t>12014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55327</t>
+          <t>53456</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87755</t>
+          <t>85505</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15062</t>
+          <t>15378</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35346</t>
+          <t>33989</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74219</t>
+          <t>75036</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112510</t>
+          <t>113224</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>263484</t>
+          <t>264173</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>307341</t>
+          <t>306610</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>187431</t>
+          <t>187174</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>218420</t>
+          <t>220440</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>463471</t>
+          <t>459712</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>516948</t>
+          <t>514383</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,01%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91809</t>
+          <t>92540</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128924</t>
+          <t>129290</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55896</t>
+          <t>55807</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84026</t>
+          <t>83772</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154412</t>
+          <t>155979</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>203302</t>
+          <t>202856</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2759</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13183</t>
+          <t>13099</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>6184</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22410</t>
+          <t>21361</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16083</t>
+          <t>17720</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14088</t>
+          <t>13753</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>9279</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25953</t>
+          <t>25833</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>40006</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65148</t>
+          <t>67212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64895</t>
+          <t>64354</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85920</t>
+          <t>85386</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123280</t>
+          <t>124558</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>205041</t>
+          <t>204338</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>242411</t>
+          <t>243784</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>216768</t>
+          <t>218143</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>253800</t>
+          <t>254526</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>432702</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>485964</t>
+          <t>489072</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,2%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66337</t>
+          <t>65053</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98401</t>
+          <t>98376</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59878</t>
+          <t>58473</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90593</t>
+          <t>89523</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133462</t>
+          <t>130869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177383</t>
+          <t>174752</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>959</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>9609</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>10948</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9499</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11023</t>
+          <t>10873</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15650</t>
+          <t>16927</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48741</t>
+          <t>50485</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78820</t>
+          <t>80268</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24257</t>
+          <t>25326</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64685</t>
+          <t>61742</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>97152</t>
+          <t>96774</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>304337</t>
+          <t>304516</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>350439</t>
+          <t>349079</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>84157</t>
+          <t>84549</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>109185</t>
+          <t>108712</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>398256</t>
+          <t>395636</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>450268</t>
+          <t>450166</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,39%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119339</t>
+          <t>119048</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>160775</t>
+          <t>158864</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34975</t>
+          <t>35852</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58433</t>
+          <t>58407</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>162091</t>
+          <t>161620</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>205141</t>
+          <t>208559</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19325</t>
+          <t>19479</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9132</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23534</t>
+          <t>24566</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21689</t>
+          <t>20345</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19204</t>
+          <t>18750</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32674</t>
+          <t>33940</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118631</t>
+          <t>117478</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>164904</t>
+          <t>160047</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>50606</t>
+          <t>50828</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>81090</t>
+          <t>81692</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>178170</t>
+          <t>179400</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>230753</t>
+          <t>233292</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>679757</t>
+          <t>682685</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>749434</t>
+          <t>748157</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>396509</t>
+          <t>394075</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>447177</t>
+          <t>448957</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1087115</t>
+          <t>1093035</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1182205</t>
+          <t>1178823</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,37%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>323354</t>
+          <t>324829</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>389448</t>
+          <t>385759</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>183630</t>
+          <t>181521</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>231322</t>
+          <t>230007</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>519891</t>
+          <t>524852</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>601091</t>
+          <t>603661</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11428</t>
+          <t>11683</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27822</t>
+          <t>28408</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19768</t>
+          <t>20542</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21487</t>
+          <t>20863</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41775</t>
+          <t>41865</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11429</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2557</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16235</t>
+          <t>15498</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21380</t>
+          <t>22628</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>33055</t>
+          <t>33644</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>59717</t>
+          <t>58892</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>21195</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>44860</t>
+          <t>43715</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>62331</t>
+          <t>60407</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>95361</t>
+          <t>97179</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>175168</t>
+          <t>177687</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>213801</t>
+          <t>216088</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>310470</t>
+          <t>311795</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>358637</t>
+          <t>360324</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>502013</t>
+          <t>502867</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>565450</t>
+          <t>564053</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,43%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>80580</t>
+          <t>80670</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>116605</t>
+          <t>114393</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>163514</t>
+          <t>164859</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>209198</t>
+          <t>209524</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>255325</t>
+          <t>254542</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>313075</t>
+          <t>314020</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>12914</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>14731</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7728</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22219</t>
+          <t>22779</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22805</t>
+          <t>24216</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>12474</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>32135</t>
+          <t>30957</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>37426</t>
+          <t>37057</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>61587</t>
+          <t>60861</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>95332</t>
+          <t>95620</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>135720</t>
+          <t>137007</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>139543</t>
+          <t>139584</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>185527</t>
+          <t>185424</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>170861</t>
+          <t>169112</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>202502</t>
+          <t>201211</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>791184</t>
+          <t>792022</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>859484</t>
+          <t>855827</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>970108</t>
+          <t>975327</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1042248</t>
+          <t>1045563</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,67%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>41137</t>
+          <t>41128</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>66711</t>
+          <t>68150</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>252696</t>
+          <t>252293</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>309457</t>
+          <t>308896</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>304024</t>
+          <t>305108</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>366443</t>
+          <t>367673</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>22445</t>
+          <t>21926</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>11065</t>
+          <t>11283</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>28871</t>
+          <t>29307</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>27627</t>
+          <t>26319</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>54974</t>
+          <t>54542</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>35424</t>
+          <t>34072</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>63434</t>
+          <t>62746</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>67930</t>
+          <t>67191</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>105749</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>372154</t>
+          <t>375480</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>455569</t>
+          <t>451211</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>271551</t>
+          <t>265397</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>334834</t>
+          <t>332758</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>666370</t>
+          <t>666682</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>770564</t>
+          <t>770850</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1880978</t>
+          <t>1874521</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1992637</t>
+          <t>1985051</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2057912</t>
+          <t>2058586</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2169845</t>
+          <t>2174743</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3970415</t>
+          <t>3974237</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4129622</t>
+          <t>4130747</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,17%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>784011</t>
+          <t>784463</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>881643</t>
+          <t>885633</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>814225</t>
+          <t>816411</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>911346</t>
+          <t>915159</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1622299</t>
+          <t>1625447</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1770573</t>
+          <t>1766892</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>34779</t>
+          <t>34672</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>63241</t>
+          <t>63118</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>35882</t>
+          <t>35152</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>63544</t>
+          <t>60698</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>76727</t>
+          <t>77486</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>115752</t>
+          <t>115777</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10923</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16677</t>
+          <t>15894</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22861</t>
+          <t>23908</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27294</t>
+          <t>26782</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49728</t>
+          <t>50124</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29611</t>
+          <t>30312</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56775</t>
+          <t>55992</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62777</t>
+          <t>61059</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98383</t>
+          <t>96563</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>234408</t>
+          <t>236451</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>280718</t>
+          <t>278738</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>172910</t>
+          <t>171154</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>210261</t>
+          <t>208782</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>423870</t>
+          <t>421948</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>480261</t>
+          <t>476804</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>63,8%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103689</t>
+          <t>104093</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>146327</t>
+          <t>142370</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50170</t>
+          <t>50602</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80008</t>
+          <t>80983</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163270</t>
+          <t>163577</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>214210</t>
+          <t>214181</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21415</t>
+          <t>21754</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10032</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9213</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27302</t>
+          <t>25460</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16200</t>
+          <t>16098</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>25226</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50536</t>
+          <t>49545</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38385</t>
+          <t>40284</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48225</t>
+          <t>48447</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81463</t>
+          <t>81744</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>230661</t>
+          <t>230902</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>275477</t>
+          <t>273723</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>196012</t>
+          <t>194354</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>232870</t>
+          <t>232982</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>440029</t>
+          <t>442418</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>497336</t>
+          <t>497629</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,93%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95535</t>
+          <t>96227</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>135168</t>
+          <t>136342</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62236</t>
+          <t>60764</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94817</t>
+          <t>92633</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>165933</t>
+          <t>167634</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>214941</t>
+          <t>215714</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,58%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15748</t>
+          <t>16033</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>9606</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26487</t>
+          <t>28082</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14468</t>
+          <t>15059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37985</t>
+          <t>37172</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28178</t>
+          <t>28142</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53599</t>
+          <t>53254</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13393</t>
+          <t>13265</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32572</t>
+          <t>32522</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46739</t>
+          <t>46670</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79322</t>
+          <t>78041</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>368367</t>
+          <t>367704</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>418960</t>
+          <t>420361</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>145546</t>
+          <t>144346</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>176891</t>
+          <t>176971</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>525364</t>
+          <t>525363</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>582261</t>
+          <t>586862</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>66,12%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>156372</t>
+          <t>156764</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>203050</t>
+          <t>203390</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56206</t>
+          <t>56815</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85691</t>
+          <t>85843</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>225383</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>276706</t>
+          <t>276674</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22248</t>
+          <t>23236</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,82 +7571,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>3942</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>16847</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>9684</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>26764</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>1,09%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3942</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>10689</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>16847</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>9985</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>27470</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11091</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28815</t>
+          <t>28867</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13506</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34090</t>
+          <t>34187</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28657</t>
+          <t>29528</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55899</t>
+          <t>55746</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>76705</t>
+          <t>76814</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>118365</t>
+          <t>116982</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>50652</t>
+          <t>50366</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>82641</t>
+          <t>81682</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>136909</t>
+          <t>136921</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>186258</t>
+          <t>184517</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>641137</t>
+          <t>640851</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>712268</t>
+          <t>708279</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424177</t>
+          <t>424662</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>478802</t>
+          <t>478200</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1084478</t>
+          <t>1081918</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1174161</t>
+          <t>1174377</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,15%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>302752</t>
+          <t>306034</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>366493</t>
+          <t>366817</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>176293</t>
+          <t>174205</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>224754</t>
+          <t>225537</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>493510</t>
+          <t>494210</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>573406</t>
+          <t>576592</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21576</t>
+          <t>21581</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44707</t>
+          <t>44491</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16426</t>
+          <t>16945</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37921</t>
+          <t>38544</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>42978</t>
+          <t>43593</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>76532</t>
+          <t>76206</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>14573</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20259</t>
+          <t>20854</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11790</t>
+          <t>10698</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30931</t>
+          <t>29188</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25615</t>
+          <t>26028</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49109</t>
+          <t>49582</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>39616</t>
+          <t>39233</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>71991</t>
+          <t>69641</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>70863</t>
+          <t>70141</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>110923</t>
+          <t>107915</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>306400</t>
+          <t>306570</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>351116</t>
+          <t>348767</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>409367</t>
+          <t>411398</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>466255</t>
+          <t>466624</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>728158</t>
+          <t>733179</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>802792</t>
+          <t>803454</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,31%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>106272</t>
+          <t>108414</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>147493</t>
+          <t>149271</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>201663</t>
+          <t>199977</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>251327</t>
+          <t>250465</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>321409</t>
+          <t>318685</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>387654</t>
+          <t>381807</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18889</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19411</t>
+          <t>20425</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>43027</t>
+          <t>40608</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>29542</t>
+          <t>31472</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>56024</t>
+          <t>56597</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15367</t>
+          <t>16618</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25601</t>
+          <t>25621</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14951</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>36947</t>
+          <t>34088</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24732</t>
+          <t>24151</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>46294</t>
+          <t>46905</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>88253</t>
+          <t>87131</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>126922</t>
+          <t>126598</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>115720</t>
+          <t>118372</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>161137</t>
+          <t>163116</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>163362</t>
+          <t>164836</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>193706</t>
+          <t>195837</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>667717</t>
+          <t>666158</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>733617</t>
+          <t>733336</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>843925</t>
+          <t>847944</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>919051</t>
+          <t>920987</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,18%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>28656</t>
+          <t>28585</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>51696</t>
+          <t>51536</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>231220</t>
+          <t>235604</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>289892</t>
+          <t>294161</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>271528</t>
+          <t>269016</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>331933</t>
+          <t>331833</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8981</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>13211</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>30918</t>
+          <t>31833</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,47 +9652,47 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>24408</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>15869</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>36248</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>24408</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>16288</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>35194</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>34312</t>
+          <t>33970</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>62119</t>
+          <t>62681</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>48908</t>
+          <t>48258</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>83492</t>
+          <t>81149</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>90203</t>
+          <t>91786</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>132826</t>
+          <t>135338</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>247848</t>
+          <t>247152</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>313612</t>
+          <t>312780</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>278331</t>
+          <t>278902</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>350638</t>
+          <t>346473</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,47 +9995,47 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>9,8%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>592665</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>546710</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>640048</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>8,53%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
           <t>7,87%</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>557</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>592665</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>545414</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>640659</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2030926</t>
+          <t>2027555</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2143450</t>
+          <t>2150496</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2100053</t>
+          <t>2104454</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2223377</t>
+          <t>2223969</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4165459</t>
+          <t>4164708</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4331093</t>
+          <t>4328836</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,28%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>864692</t>
+          <t>864827</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>971912</t>
+          <t>973023</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>840046</t>
+          <t>841524</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>952201</t>
+          <t>953852</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1742572</t>
+          <t>1743002</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1895703</t>
+          <t>1898936</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>63336</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>98844</t>
+          <t>99347</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>83243</t>
+          <t>81137</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>122960</t>
+          <t>122334</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>155303</t>
+          <t>154984</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>209637</t>
+          <t>207475</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>860</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7558</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10169</t>
+          <t>10599</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13776</t>
+          <t>14693</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33999</t>
+          <t>34178</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62941</t>
+          <t>62225</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28194</t>
+          <t>27991</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53265</t>
+          <t>51866</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67997</t>
+          <t>69447</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104851</t>
+          <t>104801</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>220042</t>
+          <t>220589</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>265421</t>
+          <t>263650</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>195877</t>
+          <t>197819</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>233926</t>
+          <t>234784</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>431646</t>
+          <t>430618</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>486507</t>
+          <t>490410</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>63,28%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107204</t>
+          <t>108836</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148358</t>
+          <t>148960</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70472</t>
+          <t>70597</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104430</t>
+          <t>103520</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>188739</t>
+          <t>188869</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>238295</t>
+          <t>241786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14816</t>
+          <t>14567</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16685</t>
+          <t>17052</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10134</t>
+          <t>9491</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15709</t>
+          <t>16027</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21828</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28460</t>
+          <t>28580</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53890</t>
+          <t>52951</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31551</t>
+          <t>30511</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56794</t>
+          <t>57463</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66158</t>
+          <t>67686</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>101711</t>
+          <t>103152</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>200722</t>
+          <t>195609</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>238221</t>
+          <t>236277</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185282</t>
+          <t>184133</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>225758</t>
+          <t>224652</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>394639</t>
+          <t>393924</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>450171</t>
+          <t>450048</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,37%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89178</t>
+          <t>90011</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123684</t>
+          <t>125411</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85062</t>
+          <t>86013</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119630</t>
+          <t>121818</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>185731</t>
+          <t>185433</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>235935</t>
+          <t>235181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13553</t>
+          <t>13387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21136</t>
+          <t>20144</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26206</t>
+          <t>27202</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14906</t>
+          <t>15228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>3932</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16927</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30170</t>
+          <t>30290</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57028</t>
+          <t>55012</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13056</t>
+          <t>12983</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30030</t>
+          <t>31597</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48430</t>
+          <t>47625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78335</t>
+          <t>77544</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>277775</t>
+          <t>279197</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>322959</t>
+          <t>325284</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>74087</t>
+          <t>73790</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>98957</t>
+          <t>101477</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>361441</t>
+          <t>363335</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>414396</t>
+          <t>415689</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,6%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>141127</t>
+          <t>137689</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>183169</t>
+          <t>179972</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42172</t>
+          <t>41310</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66766</t>
+          <t>67068</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>191105</t>
+          <t>189967</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>240056</t>
+          <t>239001</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17099</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5966</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19405</t>
+          <t>19357</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>14203</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26965</t>
+          <t>27230</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15213</t>
+          <t>15267</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35222</t>
+          <t>35448</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>86272</t>
+          <t>84491</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>123926</t>
+          <t>127165</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>72544</t>
+          <t>72750</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>170702</t>
+          <t>165908</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>222753</t>
+          <t>220668</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>586816</t>
+          <t>588570</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>653539</t>
+          <t>652998</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>405694</t>
+          <t>410908</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>465252</t>
+          <t>464176</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1006654</t>
+          <t>1009996</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1100049</t>
+          <t>1099272</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,95%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>344341</t>
+          <t>344276</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>406924</t>
+          <t>408814</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>229609</t>
+          <t>230050</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>284100</t>
+          <t>281568</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>591656</t>
+          <t>585288</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>677858</t>
+          <t>667861</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>33,99%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24955</t>
+          <t>25665</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>49863</t>
+          <t>52990</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14763</t>
+          <t>14720</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34502</t>
+          <t>34766</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>44425</t>
+          <t>44918</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>75506</t>
+          <t>75643</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17586</t>
+          <t>17454</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23854</t>
+          <t>24724</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>49833</t>
+          <t>47582</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>80052</t>
+          <t>79055</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>46969</t>
+          <t>46936</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>79186</t>
+          <t>75968</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>102535</t>
+          <t>103099</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>148224</t>
+          <t>143083</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>295081</t>
+          <t>296498</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>348538</t>
+          <t>347281</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>364160</t>
+          <t>364811</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>418300</t>
+          <t>420229</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>679148</t>
+          <t>678055</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>754270</t>
+          <t>754817</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,71%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>194024</t>
+          <t>196471</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>241448</t>
+          <t>242036</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>232172</t>
+          <t>232534</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>287815</t>
+          <t>283916</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>440141</t>
+          <t>440583</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>511818</t>
+          <t>510305</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17271</t>
+          <t>16986</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>27804</t>
+          <t>27957</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>17840</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>39054</t>
+          <t>38934</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -14138,7 +14138,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13959</t>
+          <t>13478</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26373</t>
+          <t>25415</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14821</t>
+          <t>14075</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>34362</t>
+          <t>32962</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>30514</t>
+          <t>31854</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>55824</t>
+          <t>55464</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>78648</t>
+          <t>78103</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>116423</t>
+          <t>116882</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>118164</t>
+          <t>118673</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>165040</t>
+          <t>161946</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>137662</t>
+          <t>138271</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>171581</t>
+          <t>171607</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>559715</t>
+          <t>558737</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>624969</t>
+          <t>630002</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>711384</t>
+          <t>710612</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>785765</t>
+          <t>790704</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>59198</t>
+          <t>59173</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>89636</t>
+          <t>88115</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>313597</t>
+          <t>313096</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>377589</t>
+          <t>378139</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>381347</t>
+          <t>380824</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>454271</t>
+          <t>451610</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>13054</t>
+          <t>13977</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>18723</t>
+          <t>18720</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>39322</t>
+          <t>39645</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>24360</t>
+          <t>23078</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>49253</t>
+          <t>47711</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>23191</t>
+          <t>24391</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>47007</t>
+          <t>46434</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>41134</t>
+          <t>43113</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>73234</t>
+          <t>72100</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>72206</t>
+          <t>70508</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>111154</t>
+          <t>108356</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>305829</t>
+          <t>307340</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>375854</t>
+          <t>375626</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,7 +14968,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>311605</t>
+          <t>315669</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>385975</t>
+          <t>389078</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>635497</t>
+          <t>638256</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>743408</t>
+          <t>739880</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1798106</t>
+          <t>1798389</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1913493</t>
+          <t>1916487</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1870610</t>
+          <t>1869265</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1991353</t>
+          <t>1990860</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3705386</t>
+          <t>3713678</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3875900</t>
+          <t>3875108</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,25%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1009839</t>
+          <t>1012513</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1123681</t>
+          <t>1119936</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1043324</t>
+          <t>1036345</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1160141</t>
+          <t>1150514</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2081935</t>
+          <t>2080703</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2237373</t>
+          <t>2232205</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>57984</t>
+          <t>58935</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>93084</t>
+          <t>92540</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>67670</t>
+          <t>65567</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>105434</t>
+          <t>102875</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>133112</t>
+          <t>133802</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>188103</t>
+          <t>186585</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
